--- a/doc/templates/Hango_Question_Bank_Import_Template.xlsx
+++ b/doc/templates/Hango_Question_Bank_Import_Template.xlsx
@@ -11,11 +11,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="SkillTypeList">Lists!$A$1:$A$26</definedName>
     <definedName name="DifficultyList">Lists!$B$1:$B$4</definedName>
     <definedName name="GroupTypeList">Lists!$C$1:$C$6</definedName>
+    <definedName name="SkillTypeList">Lists!$A$1:$A$27</definedName>
   </definedNames>
-  <calcPr calcId="181029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -151,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -187,12 +187,80 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -490,7 +558,8 @@
   <cols>
     <col width="114" customWidth="1" style="4" min="1" max="1"/>
     <col width="68.296875" customWidth="1" style="4" min="2" max="2"/>
-    <col width="9" customWidth="1" style="4" min="3" max="16384"/>
+    <col width="9" customWidth="1" style="4" min="3" max="3"/>
+    <col width="9" customWidth="1" style="4" min="4" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.8" customFormat="1" customHeight="1" s="1">
@@ -500,10 +569,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22.8" customHeight="1">
+    <row r="2" ht="22.8" customHeight="1" s="19">
       <c r="A2" s="6" t="n"/>
     </row>
-    <row r="3" ht="15.6" customHeight="1">
+    <row r="3" ht="15.6" customHeight="1" s="19">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1. This file is used to import the entire question bank structure (Questions)</t>
@@ -511,11 +580,11 @@
       </c>
       <c r="B3" s="8" t="n"/>
     </row>
-    <row r="4" ht="15" customHeight="1">
+    <row r="4" ht="15" customHeight="1" s="19">
       <c r="A4" s="9" t="n"/>
       <c r="B4" s="8" t="n"/>
     </row>
-    <row r="5" ht="15.6" customHeight="1">
+    <row r="5" ht="15.6" customHeight="1" s="19">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>2. Sheets to fill in:</t>
@@ -523,7 +592,7 @@
       </c>
       <c r="B5" s="8" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" ht="15" customHeight="1" s="19">
       <c r="A6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">   - Question: List of question (about single question or group question)</t>
@@ -531,11 +600,11 @@
       </c>
       <c r="B6" s="8" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" ht="15" customHeight="1" s="19">
       <c r="A7" s="15" t="n"/>
       <c r="B7" s="8" t="n"/>
     </row>
-    <row r="8" ht="15.6" customHeight="1">
+    <row r="8" ht="15.6" customHeight="1" s="19">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>3. Important Rules:</t>
@@ -567,7 +636,7 @@
       </c>
       <c r="B11" s="11" t="n"/>
     </row>
-    <row r="12" ht="14.4" customHeight="1">
+    <row r="12" ht="14.4" customHeight="1" s="19">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   - Order Index must be greater than 0, and the order of questions must not be duplicated</t>
@@ -603,7 +672,7 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">      + Phonetics</t>
+          <t xml:space="preserve">      + Part of speech / Participle</t>
         </is>
       </c>
       <c r="B16" s="11" t="n"/>
@@ -942,18 +1011,18 @@
   <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.8984375" defaultRowHeight="13.8"/>
   <cols>
-    <col width="15.19921875" customWidth="1" min="1" max="1"/>
-    <col width="14.09765625" customWidth="1" min="2" max="2"/>
-    <col width="22.09765625" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="17.8984375" customWidth="1" min="10" max="10"/>
-    <col width="14.3984375" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="15.19921875" customWidth="1" style="19" min="1" max="1"/>
+    <col width="14.09765625" customWidth="1" style="19" min="2" max="2"/>
+    <col width="22.09765625" customWidth="1" style="19" min="3" max="3"/>
+    <col width="20" customWidth="1" style="19" min="4" max="7"/>
+    <col width="15" customWidth="1" style="19" min="8" max="8"/>
+    <col width="18" customWidth="1" style="19" min="9" max="9"/>
+    <col width="17.8984375" customWidth="1" style="19" min="10" max="10"/>
+    <col width="14.3984375" customWidth="1" style="19" min="11" max="11"/>
+    <col width="16" customWidth="1" style="19" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.8" customHeight="1">
+    <row r="1" ht="22.8" customHeight="1" s="19">
       <c r="B1" s="18" t="inlineStr">
         <is>
           <t>QUESTIONS</t>
@@ -1022,32 +1091,32 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="19.95" customHeight="1"/>
-    <row r="4" ht="19.95" customHeight="1"/>
-    <row r="5" ht="19.95" customHeight="1"/>
-    <row r="6" ht="19.95" customHeight="1"/>
-    <row r="7" ht="19.95" customHeight="1"/>
-    <row r="8" ht="19.95" customHeight="1"/>
-    <row r="9" ht="19.95" customHeight="1"/>
-    <row r="10" ht="19.95" customHeight="1"/>
-    <row r="11" ht="19.95" customHeight="1"/>
-    <row r="12" ht="19.95" customHeight="1"/>
-    <row r="13" ht="19.95" customHeight="1"/>
-    <row r="14" ht="19.95" customHeight="1"/>
-    <row r="15" ht="19.95" customHeight="1"/>
+    <row r="3" ht="19.95" customHeight="1" s="19"/>
+    <row r="4" ht="19.95" customHeight="1" s="19"/>
+    <row r="5" ht="19.95" customHeight="1" s="19"/>
+    <row r="6" ht="19.95" customHeight="1" s="19"/>
+    <row r="7" ht="19.95" customHeight="1" s="19"/>
+    <row r="8" ht="19.95" customHeight="1" s="19"/>
+    <row r="9" ht="19.95" customHeight="1" s="19"/>
+    <row r="10" ht="19.95" customHeight="1" s="19"/>
+    <row r="11" ht="19.95" customHeight="1" s="19"/>
+    <row r="12" ht="19.95" customHeight="1" s="19"/>
+    <row r="13" ht="19.95" customHeight="1" s="19"/>
+    <row r="14" ht="19.95" customHeight="1" s="19"/>
+    <row r="15" ht="19.95" customHeight="1" s="19"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:L1"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="J3:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Skill Type" error="Please select a valid Skill Type from the list." promptTitle="Skill Type" prompt="Choose a Skill Type from the dropdown list." type="list">
-      <formula1>=SkillTypeList</formula1>
+      <formula1>SkillTypeList</formula1>
     </dataValidation>
     <dataValidation sqref="K3:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Difficulty" error="Please select a valid Difficulty from the list." promptTitle="Difficulty" prompt="Choose a Difficulty from the dropdown list." type="list">
-      <formula1>=DifficultyList</formula1>
+      <formula1>DifficultyList</formula1>
     </dataValidation>
     <dataValidation sqref="L3:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Group Type" error="Please select a valid Group Type from the list." promptTitle="Group Type" prompt="Choose a Group Type from the dropdown list." type="list">
-      <formula1>=GroupTypeList</formula1>
+      <formula1>GroupTypeList</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1060,8 +1129,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1307,6 +1376,13 @@
       <c r="A26" t="inlineStr">
         <is>
           <t>Sentence insertion</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Part of speech / Participle</t>
         </is>
       </c>
     </row>
